--- a/results/job_matches_2026-10-05.xlsx
+++ b/results/job_matches_2026-10-05.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,35 +456,385 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>La Familia Medical Center</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aacae00553886f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>VMware VCF Administrator</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>First Advantage</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Tignall, GA, US USA</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>12.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Azure, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8730f563dbd095d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gresham, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e3de17edd4ad1a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad13a494d02abc38</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8239bcbad42324d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0fbdd427d11bc16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc834c9ee6721d0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb2e02e288febf1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd19dd1a372112c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6323346dc303f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Analyst</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b74e19cc7dd3843</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-05.xlsx
+++ b/results/job_matches_2026-10-05.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Data Engineer, Data Management &amp; BI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>La Familia Medical Center</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aacae00553886f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52dec15d92eb10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VMware VCF Administrator</t>
+          <t>Data Engineer III AI, Automation, &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Advantage</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tignall, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8730f563dbd095d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b965769d33666ec</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3de17edd4ad1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3a53bca427f9bc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Managing Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad13a494d02abc38</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f0324e9bc372ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>La Familia Medical Center</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8239bcbad42324d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6aacae00553886f3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Medallion Architecture</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0fbdd427d11bc16</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad2431edc28d94e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc834c9ee6721d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b016308efc3eae2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2e02e288febf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=299b4bbe67f91792</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd19dd1a372112c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a78c8e54c1f97</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,42 +799,427 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6323346dc303f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=a15dd7b9cef5a234</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ed2691989b708f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bd44e886a3ff4ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wakefield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7013b6133945b032</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0da7fcfc987a7ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=600e123842bacfc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Data Analyst - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6b1fb40eeb66f17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>isolved</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53183509479236f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>isolved</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9468ea1e9b04ea28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VMware VCF Administrator</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>First Advantage</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tignall, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8730f563dbd095d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, NoSQL, ELT, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7be1b9b5bc867059</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer / Platform Administrator (Azure Databricks)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vanderbilt Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>11.1</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Power BI, Splunk, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b74e19cc7dd3843</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MS Excel, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d60ae2a8e1708a08</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jackson, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Spark, PySpark, Oracle, MySQL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7b198bf0f349ae</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-05.xlsx
+++ b/results/job_matches_2026-10-05.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,12 +526,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Managing Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -540,11 +540,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3a53bca427f9bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f0324e9bc372ed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Managing Engineer, Data Engineering</t>
+          <t>AI Enterprise Architect-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f0324e9bc372ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3d45a3054cc31c</t>
         </is>
       </c>
     </row>
@@ -666,25 +666,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Commercial DT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b016308efc3eae2</t>
+          <t>https://www.indeed.com/viewjob?jk=eec85fd3b937ce66</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299b4bbe67f91792</t>
+          <t>https://www.indeed.com/viewjob?jk=c956f1cdfac97bda</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst / Analytics Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>VASERJOB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a78c8e54c1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bc1ca87aba01e9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Meetic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15dd7b9cef5a234</t>
+          <t>https://www.indeed.com/viewjob?jk=c7952341ee0c6ac4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Analyst - Agentic AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2691989b708f3</t>
+          <t>https://www.indeed.com/viewjob?jk=819ad471f98483cc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd44e886a3ff4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=21f0317152441f3f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Engineer, Karat Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7013b6133945b032</t>
+          <t>https://www.indeed.com/viewjob?jk=4503e534007dd850</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0da7fcfc987a7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9b016308efc3eae2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600e123842bacfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=299b4bbe67f91792</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Data Analyst - Agentic AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b1fb40eeb66f17</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a78c8e54c1f97</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53183509479236f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15dd7b9cef5a234</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,67 +1079,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9468ea1e9b04ea28</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2691989b708f3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VMware VCF Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>First Advantage</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tignall, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8730f563dbd095d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd44e886a3ff4ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, NoSQL, ELT, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be1b9b5bc867059</t>
+          <t>https://www.indeed.com/viewjob?jk=7013b6133945b032</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer / Platform Administrator (Azure Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vanderbilt Health</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MS Excel, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,42 +1184,1022 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60ae2a8e1708a08</t>
+          <t>https://www.indeed.com/viewjob?jk=a0da7fcfc987a7ea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=600e123842bacfc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Data Analyst - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6b1fb40eeb66f17</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5425f278842298</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Solutions Architect (Contract)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sound Physicians</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Dataflow, Scala, Snowflake, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ca6d8b53f7fae1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data &amp; Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Integrated Financial Settlements</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=870e38fac0b2d478</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Managing Engineer, Software Engineering -Remote</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bb172bb48712256</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Jackson, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f5b52e17a5bd63e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer-3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33bb747e2908314c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. People Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b92e55014f77298b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Triconn Solutions</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=985b7795e94b06ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arecibo, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f552257cba93bb49</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Qbitech</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea14e8ca5424e9cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr. Data Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DoubleVerify</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc6dc0fbf3996a4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Data Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DoubleVerify</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=708e5d96e2689486</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>isolved</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53183509479236f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>isolved</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9468ea1e9b04ea28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Expert Analyst Data Management (Epic ODBA Certification Req'd)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fort Washington, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Terraform</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3967305210de342a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe90612a7cd40771</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=653ba6f45e27b32b</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Platform Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>11.1</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Spark, PySpark, Oracle, MySQL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7b198bf0f349ae</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9ff7692093a84ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DevSecOps Engineer (R0172063) - (SSFB/HSV) (2 Positions)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>INNOVIM DEFENSE SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b39435d6c83f900a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Wilson Language Training Corp.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=206b79ebbffc09e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Java GraphQL Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66d2947e2f320192</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2748f5c3e0997c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b748bf2b91e4a02e</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Quality Assurance Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Federal Reserve Bank of St. Louis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33a4e4327114b742</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (1042) – Department of Technology</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>City and County of San Francisco</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe04b5d2de255308</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>IT Analyst</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>New Era Cap, LLC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53936ef2d1bc5e64</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AEP Middleware Pod Kafka Admin</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, Kafka Connect, Snowflake, Oracle, Splunk, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7c7915433a059ea</t>
         </is>
       </c>
     </row>
